--- a/库存清单.xlsx
+++ b/库存清单.xlsx
@@ -746,18 +746,18 @@
       </c>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>不足</t>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>充足</t>
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         <v>10.5</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>31.5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
@@ -2419,19 +2419,19 @@
         <v>9</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>423.5</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4">
@@ -2519,19 +2519,19 @@
         <v>29</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>981.5</v>
+        <v>1034</v>
       </c>
     </row>
   </sheetData>
@@ -2548,7 +2548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3275,27 +3275,27 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>ST-001</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>内衣</t>
+          <t>裤袜</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>无钢圈舒适文胸</t>
+          <t>发热保暖连裤袜</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>36B</t>
+          <t>L-LL</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>肤色</t>
+          <t>深灰</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Triumph SG</t>
+          <t>Gunze 日本</t>
         </is>
       </c>
     </row>
@@ -3331,22 +3331,22 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>L-LL</t>
+          <t>M-L</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>深灰</t>
+          <t>黑色</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
@@ -3357,22 +3357,22 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>ST-001</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>裤袜</t>
+          <t>内衣</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>发热保暖连裤袜</t>
+          <t>无钢圈舒适文胸</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>M-L</t>
+          <t>34B</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3381,24 +3381,24 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Gunze 日本</t>
+          <t>Triumph SG</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>BR-004</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3408,70 +3408,29 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>无钢圈舒适文胸</t>
+          <t>聚拢调整型文胸</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>34B</t>
+          <t>36C</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>黑色</t>
+          <t>肤色</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>Triumph SG</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>BR-004</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>内衣</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>聚拢调整型文胸</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>36C</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>肤色</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Wacoal 代理</t>
         </is>

--- a/库存清单.xlsx
+++ b/库存清单.xlsx
@@ -38,11 +38,11 @@
       <sz val="11"/>
     </font>
     <font>
+      <color rgb="002F5496"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00ED7D31"/>
-    </font>
-    <font>
-      <color rgb="002F5496"/>
     </font>
     <font>
       <b val="1"/>
@@ -630,18 +630,18 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>8</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>不足</t>
+          <t>充足</t>
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         <v>10.5</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>52.5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4">
@@ -693,7 +693,7 @@
       <c r="I4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -751,7 +751,7 @@
       <c r="I5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>充足</t>
         </is>
@@ -813,7 +813,7 @@
       <c r="I6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>充足</t>
         </is>
@@ -871,7 +871,7 @@
       <c r="I7" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -933,7 +933,7 @@
       <c r="I8" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>充足</t>
         </is>
@@ -991,7 +991,7 @@
       <c r="I9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>充足</t>
         </is>
@@ -1049,7 +1049,7 @@
       <c r="I10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>充足</t>
         </is>
@@ -1107,7 +1107,7 @@
       <c r="I11" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>充足</t>
         </is>
@@ -1165,7 +1165,7 @@
       <c r="I12" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -1227,7 +1227,7 @@
       <c r="I13" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -1285,7 +1285,7 @@
       <c r="I14" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -1343,7 +1343,7 @@
       <c r="I15" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -1405,7 +1405,7 @@
       <c r="I16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -1463,7 +1463,7 @@
       <c r="I17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -1525,7 +1525,7 @@
       <c r="I18" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -1587,7 +1587,7 @@
       <c r="I19" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>充足</t>
         </is>
@@ -1645,7 +1645,7 @@
       <c r="I20" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -1703,7 +1703,7 @@
       <c r="I21" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -1761,7 +1761,7 @@
       <c r="I22" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J22" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -1819,7 +1819,7 @@
       <c r="I23" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>充足</t>
         </is>
@@ -1877,7 +1877,7 @@
       <c r="I24" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -1939,7 +1939,7 @@
       <c r="I25" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -2001,7 +2001,7 @@
       <c r="I26" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -2063,7 +2063,7 @@
       <c r="I27" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="J27" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -2125,7 +2125,7 @@
       <c r="I28" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="J28" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -2183,7 +2183,7 @@
       <c r="I29" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="J29" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -2245,7 +2245,7 @@
       <c r="I30" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J30" s="6" t="inlineStr">
         <is>
           <t>不足</t>
         </is>
@@ -2307,7 +2307,7 @@
       <c r="I31" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="J31" s="6" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>充足</t>
         </is>
@@ -2419,19 +2419,19 @@
         <v>9</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>476</v>
+        <v>528.5</v>
       </c>
     </row>
     <row r="4">
@@ -2519,19 +2519,19 @@
         <v>29</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>1034</v>
+        <v>1086.5</v>
       </c>
     </row>
   </sheetData>
@@ -2548,7 +2548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2648,7 +2648,7 @@
       <c r="G3" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="6" t="n">
         <v>19</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -2689,7 +2689,7 @@
       <c r="G4" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="6" t="n">
         <v>19</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -2730,7 +2730,7 @@
       <c r="G5" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="6" t="n">
         <v>19</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -2771,7 +2771,7 @@
       <c r="G6" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="6" t="n">
         <v>19</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -2812,7 +2812,7 @@
       <c r="G7" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="6" t="n">
         <v>12</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -2853,7 +2853,7 @@
       <c r="G8" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="6" t="n">
         <v>12</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -2894,7 +2894,7 @@
       <c r="G9" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="6" t="n">
         <v>12</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -2935,7 +2935,7 @@
       <c r="G10" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="6" t="n">
         <v>12</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -2976,7 +2976,7 @@
       <c r="G11" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="6" t="n">
         <v>12</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -3017,7 +3017,7 @@
       <c r="G12" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="6" t="n">
         <v>12</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -3058,7 +3058,7 @@
       <c r="G13" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="6" t="n">
         <v>12</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -3099,7 +3099,7 @@
       <c r="G14" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="6" t="n">
         <v>12</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -3140,7 +3140,7 @@
       <c r="G15" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="6" t="n">
         <v>8</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -3181,7 +3181,7 @@
       <c r="G16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="6" t="n">
         <v>7</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -3222,7 +3222,7 @@
       <c r="G17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="6" t="n">
         <v>7</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -3263,7 +3263,7 @@
       <c r="G18" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="6" t="n">
         <v>5</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -3304,7 +3304,7 @@
       <c r="G19" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="6" t="n">
         <v>5</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -3345,7 +3345,7 @@
       <c r="G20" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="6" t="n">
         <v>4</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -3357,7 +3357,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>BR-004</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3367,70 +3367,29 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>无钢圈舒适文胸</t>
+          <t>聚拢调整型文胸</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>34B</t>
+          <t>36C</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>黑色</t>
+          <t>肤色</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>Triumph SG</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>BR-004</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>内衣</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>聚拢调整型文胸</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>36C</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>肤色</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>Wacoal 代理</t>
         </is>

--- a/库存清单.xlsx
+++ b/库存清单.xlsx
@@ -688,18 +688,18 @@
       </c>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>不足</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>充足</t>
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>10.5</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>31.5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5">
@@ -2419,19 +2419,19 @@
         <v>9</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>528.5</v>
+        <v>581</v>
       </c>
     </row>
     <row r="4">
@@ -2519,19 +2519,19 @@
         <v>29</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>1086.5</v>
+        <v>1139</v>
       </c>
     </row>
   </sheetData>
@@ -2548,7 +2548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3234,27 +3234,27 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>ST-001</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>内衣</t>
+          <t>裤袜</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>无钢圈舒适文胸</t>
+          <t>发热保暖连裤袜</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>34C</t>
+          <t>L-LL</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>黑色</t>
+          <t>深灰</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Triumph SG</t>
+          <t>Gunze 日本</t>
         </is>
       </c>
     </row>
@@ -3290,22 +3290,22 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>L-LL</t>
+          <t>M-L</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>深灰</t>
+          <t>黑色</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -3316,80 +3316,39 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>ST-001</t>
+          <t>BR-004</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>裤袜</t>
+          <t>内衣</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>发热保暖连裤袜</t>
+          <t>聚拢调整型文胸</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>M-L</t>
+          <t>36C</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>黑色</t>
+          <t>肤色</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="H20" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>Gunze 日本</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>BR-004</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>内衣</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>聚拢调整型文胸</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>36C</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>肤色</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>Wacoal 代理</t>
         </is>

--- a/库存清单.xlsx
+++ b/库存清单.xlsx
@@ -517,7 +517,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>服装档口 · 库存清单  |  更新日期: 2026-06-16</t>
+          <t>服装档口 · 库存清单  |  更新日期: 2026-06-17</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>8</v>
@@ -950,7 +950,7 @@
         <v>5</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>8</v>
@@ -1066,7 +1066,7 @@
         <v>5</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>8</v>
@@ -1124,7 +1124,7 @@
         <v>5</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -2368,7 +2368,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>按品类汇总  |  2026-06-16</t>
+          <t>按品类汇总  |  2026-06-17</t>
         </is>
       </c>
     </row>
@@ -2419,10 +2419,10 @@
         <v>9</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>1</v>
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>581</v>
+        <v>551</v>
       </c>
     </row>
     <row r="4">
@@ -2519,10 +2519,10 @@
         <v>29</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>18</v>
@@ -2531,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>1139</v>
+        <v>1109</v>
       </c>
     </row>
   </sheetData>
@@ -2565,7 +2565,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>低于安全线的SKU  |  2026-06-16</t>
+          <t>低于安全线的SKU  |  2026-06-17</t>
         </is>
       </c>
     </row>
